--- a/ashley_product_results.xlsx
+++ b/ashley_product_results.xlsx
@@ -413,48 +413,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:Q199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>sku</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Product Name</t>
+          <t>Landing page</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>imageSet</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Rating</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Product URL</t>
-        </is>
-      </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>SKU Valid</t>
+          <t>Series Name</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>UPC</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>cartonDepthInches</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>cartonHeightInches</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>cartonVolumeCuFeet</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>cartonWidthInches</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>chairQtyPerCarton</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>unitDepthInches</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>unitFriendlyDimensionsInches</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>unitHeightInches</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>unitWidthInches</t>
         </is>
       </c>
     </row>
@@ -466,33 +511,5999 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ryandale Accent Table</t>
+          <t>https://www.ashleyfurniture.com/p/ryandale_accent_table/A4000462.html</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$249.99</t>
+          <t>https://cdn.ashley.com/assets/A4000462.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000462-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000462-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000462-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://www.ashleyfurniture.com/p/ryandale_accent_table/A4000462.html</t>
-        </is>
-      </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
+          <t>Classic in design with a dash of textural appeal, the Ryandale accent table provides both flair and function. The glass tabletop offers the perfect perch for a lamp, while the white marble lower shelf is ideal for resting trendy coffee table books and other decorative pieces. An antiqued black finish on the frame has an edgy look that remains versatile, suiting spaces from casual to contemporary.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Antique Black</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>249.99</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Ryandale</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>24052807202</v>
+      </c>
+      <c r="I2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>20.75"</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>20.75" W x 20.75" D x 24.75" H</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>24.75"</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>20.75"</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>R407751</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/bachus_710_x_10_area_rug/R407751.html</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/R407751-4X3-CROP.jpg?fit=bounds&amp;width=1920&amp;height=1440&amp;quality=90&amp;format=webp</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bachus 7'10" x 10' Area Rug</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>299.99</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bachus</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>24052944495</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>120.00"</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>93.50" W x 120.00" D x 0.25" H</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.25"</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>93.50"</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R407681</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/bachby_710_x_10_area_rug/R407681.html</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>284.99</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bachby</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>24052944372</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>119.00"</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>94.00" W x 119.00" D x 0.25" H</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.25"</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>94.00"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4840408</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3130508</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PC3560308</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5940408</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PC2770408</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3130408</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PC5910608</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>M20121</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/peak_2.0_bonnell_full_mattress/M20121.html</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/M20131.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20131-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20131-ANGLE-ALT-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20131-TOP-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/ExplMattLayersCopy_M20131-1.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20131-ALT.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20131-M8X232-VERTICAL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20131-M8X232-HORIZONTAL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20131_Exploded-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/25Q3_AGRAC_AshleySleep_FAB_Ashcom_M201_ImageSet_2573x1050.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Pure sleep perfection. With the Peak 2.0 Bonnell full mattress, restorative rest is easier than ever. You can snooze soundly on its layers of comforting quilt foam and luxury loft fiber. A classic Bonnell coil unit and supple base foam provide the support you need. And the mattress is topped with a Hyper Cool cover, helping to keep your temperature regulated through the night.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>299</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Peak 2.0 Bonnell</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>24052925449</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>53.00"</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>74.50" W x 53.00" D x 8.00" H</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>8.00"</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>74.50"</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>M20411</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/peak_2.0_8_memory_foam_twin_mattress/M20411.html</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/M20431.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20431-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20431-ANGLE-ALT-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20431-TOP-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20431-ALT.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20431-M8X232-VERTICAL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20431-M8X232-HORIZONTAL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/ExplMattLayersCopy_M20431.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/25Q3_AGRAC_AshleySleep_FAB_Ashcom_M204_ImageSet_2573x1050.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Pure sleep perfection. With the Peak 2.0 twin mattress, restorative rest is easier than ever. Its high-density memory foam conforms to your body, delivering amazing support and comfort. A super-thick layer of firm support foam helps reduce motion transfer, so you and your partner can enjoy an undisturbed slumber. And it's topped with a stretch knit cover for durability.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>279</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Peak 2.0 8 Memory Foam</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>24052925654</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>38.00"</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>74.50" W x 38.00" D x 8.00" H</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>8.00"</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>74.50"</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M20211</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/peak_2.0_10_hybrid_twin_mattress/M20211.html</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/M20231.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20231-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20231-ANGLE-ALT-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20231-TOP-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20231-ALT.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20231-M8X232-HORIZONTAL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20231-M8X232-VERTICAL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/M20231_Exploded-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/ExplMattLayersCopy_M20231.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/25Q3_AGRAC_AshleySleep_FAB_Ashcom_M202_ImageSet_2573x1050.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Pure sleep perfection. With the Peak 2.0 hybrid twin mattress, restorative rest is easier than ever. You can snooze soundly on its layers of comforting quilt foam and luxury loft fiber. A wrapped coil unit and supple base foam provide the support you need while reducing motion transfer. And the mattress is topped with a Hyper Cool cover, helping to keep your temperature regulated through the night.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>279</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Peak 2.0 10 Hybrid</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>24052925517</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>38.00"</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>74.50" W x 38.00" D x 10.00" H</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>10.00"</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>74.50"</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>R407171</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/gailmore_8_x_10_rug/R407171.html</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/R407172-1-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407172-1-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407172-1-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407172-1-ROLL-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>We think you'll love the Gailmore rug as much as we do. A beautiful way to define your space, its gorgeous geometric design in nicely neutral tones infuses a modern sensibility that simply suits your style. And how about that plush woven shag pile that feels oh-so-good?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Cream/Pink/Ocher</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>229.99</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Gailmore</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>24052914078</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>121.00"</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>93.63" W x 121.00" D x 1.00" H</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1.00"</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>93.63"</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R407181</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/flynnwick_8_x_10_rug/R407181.html</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/R407182-1-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407182-1-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407182-1-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407182-1-ROLL-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>It feels awfully good to sink your toes into the high-pile plushness of the contemporary Flynnwick rug. With its eye-catching design, this floor centerpiece brings a sense of shag softness and geometric flair that sets your home apart.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cream/Pink/Gray</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>229.99</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Flynnwick</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>24052914092</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>120.25"</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>93.75" W x 120.25" D x 1.00" H</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1.00"</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>93.75"</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A4000612</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/cormmet_accent_table/A4000612.html</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/A4000612.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000612-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000612-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000612-SIDE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000612-TOP-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000612-FINISH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>With its sculptural form, the Cormmet accent table suits your living room’s elevated character. Your artistic point of view is reflected in its oblong design, with the mixed-material construction lending an almost industrial edge. Stunning as a standalone piece, it looks equally as chic when displaying decorative accents.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Brown/Black</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>189.99</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cormmet</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>24052871500</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>13.00"</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>19.88" W x 13.00" D x 21.00" H</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>21.00"</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>19.88"</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>R407722</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/jaseena_5_x_7_area_rug/R407722.html</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/R407722-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407722-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407722-1-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407722-1-ROLL-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407722-SWATCH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A go-with-the-flow sensibility. With abstract shapes and a simply soothing color palette, the Jaseena rug is making waves for casual style. Its plush wool and bamboo textile blend masters the art of clean-chic style with a soft touch.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Beige/Tan</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>249.99</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Jaseena</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>24052944464</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>84.00"</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>61.00" W x 84.00" D x 0.63" H</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.63"</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>61.00"</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T167-13</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/wrenwich_table_set_of_3/T167-13.html</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/T167-13-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T167-13-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T167-13-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T167-13-CT-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T167-13-END-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T167-13-BASE-FINISH.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T167-13-TOP-FINISH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Round out your seating area with the Wrenwich table set. The clean-lined profile is simple, yet striking—while the faux Carrara marble tops are anything but ordinary. Black tubular metal frames, along with open storage shelves with a light natural wood grain pattern, work beautifully together from every angle.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Brown/Black/White</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Wrenwich</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>24052915099</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>34.00"</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>34.00" W x 34.00" D x 18.13" H</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>18.13"</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>34.00"</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>L235851</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/veraleigh_floor_lamp/L235851.html</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/L235851-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/L235851-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/L235851-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/L235851-SWATCH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Add flair to your lair with the striking Veraleigh floor lamp. With a distinctive scalloped design and a fresh white finish, it’s cool from every angle. And its versatile style looks right at home everywhere from contemporary places to casual spaces. The matching table lamp is also a bright idea.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>259.99</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Veraleigh</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>24052933550</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>23.00"</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>23.00" W x 23.00" D x 66.00" H</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>66.00"</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>23.00"</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>R407551</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/turinwith_710_x_910_area_rug/R407551.html</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ivory/Black</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Turinwith</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>24052944174</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>R407691</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/fuadwick_710_x_10_area_rug/R407691.html</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fuadwick</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>24052944396</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>R407321</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/maconville_large_rug/R407321.html</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/R407321-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407321-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407322-1-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407322-1-ROLL-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407321-SWATCH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Define a space in a beautiful way with the magnificent Maconville rug. Its gorgeous geometric design in gray and ivory infuses a modern sensibility that simply suits your style without being overwhelming. Plus the rug's plush pile feels fantastic underfoot.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ivory/Gray</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Maconville</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>24052925227</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T667-6</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/tanidore_end_table/T667-6.html</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/T667-6.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T667-6-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T667-6-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T667-6-TOP-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T667-6-TOP-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T667-8-6-FINISH.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Not only does the stunning Tanidore end table enhance the aesthetic of your home, but it also provides practicality and functionality. Crafted with a mango wood frame and natural marble top, its solid construction and durable materials ensure years of reliable use. It's the perfect blend of contemporary style and timeless elegance.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Warm Brown</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tanidore</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>24052903584</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T173-13</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/pearlox_table_set_of_3/T173-13.html</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/T173-13.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T173-13-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T173-13-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T173-13-ET-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T173-13-CT-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/29203-38-35-25-T173-13.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Chic and sleek, the Pearlox table set satisfies your taste for casual contemporary design. The luxurious goldtone frames and glass tops exemplify simple sophistication. Adorn these tables with an array of art books, fresh flowers and chic trinkets for a stunning style statement.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>219.95</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pearlox</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>24052934663</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A4000611</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/keithwell_accent_table/A4000611.html</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/A4000611.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000611-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000611-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000611-SIDE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000611-BACK-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000611-TOP-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000611-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000611-FINISH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Style to aspire to. The Keithwell accent table appeals to your eye for artisanal design at an affordable price. The all-marble construction makes it a sculptural addition to your curated space. Whether this table is standing alone or with decor on its smooth top, the beauty of natural stone makes a stunning impression.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>179.99</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Keithwell</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>24052871494</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>D446-15</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/pharwynn_dining_table/D446-15.html</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/D446-15.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/D446-15-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/D446-15-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/D446-15-TOP-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/D446-15-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/D446-15-02(4).jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/D446-15-Pharwynn-DIM.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/D446-SWATCH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>You’ll love the way the Pharwynn table masterfully complements the mod vibe of your dining room. A metal frame in a sleek gunmetal color adds eye-catching contemporary flair to the casual design. Made with everyday function in mind, its small stature expertly suits dining areas limited on space.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pharwynn</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>24052905274</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>R407862</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/deenbury_5_x_7_area_rug/R407862.html</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/R407862-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407862-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407862-1-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407862-1-ROLL-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407862-SWATCH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Artisanal design makes the Deenbury area rug exceptionally alluring. Its richly hand tufted wool pile is pure pleasure. And the flowing abstract pattern in ivory, green and brown brings an organically beautiful feel to your decor.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ivory/Green/Brown</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Deenbury</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>24052944624</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>R407712</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/lisgrove_5_x_7_area_rug/R407712.html</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/R407712-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407712-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407712-1-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407712-1-ROLL-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407712-SWATCH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>The Lisgrove area rug reflects your love of approachable, clean-lined design. Its loosely structured stripes and organic hues bring a naturally beautiful element to your decor. Stage it beneath a sofa or in the bedroom for a subtle pop of pattern.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Tan/Brown/White</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lisgrove</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>24052944440</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T139-13</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/dorylin_table_set_of_3/T139-13.html</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/T139-13.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T139-13-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T139-13-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T139-13-CT-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T139-13-ET-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T139-13-MOOD.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Sleek contemporary style, meet modern versatility. The Dorylin table set upgrades living room lounging with an added dose of form and function. Clean-lined black metal frames are topped with black glass tops for monochromatic appeal. And with a coffee table and two end tables included, you can add chic convenience sofa-side and to the center of your seating area all at once.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>249.99</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dorylin</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>24052934649</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A8000499</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/floymour_wall_art/A8000499.html</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/U12300-58-46-62-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A8000499-HEAD-ON-A-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A8000499-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A8000499-HEAD-ON-B-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A8000499-HEAD-ON-C-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A8000499-HEAD-ON-D-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A8000499-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A8000499-BACK-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A8000499-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A8000499-SWATCH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Muted tones make a big visual impact in the Floymour wall art. Exuding a modern sensibility, its hand painted abstract design brings dynamic visual interest to your decor while remaining subtle in style. Hang it solo as a statement piece, or make it the focal point of a chic gallery wall.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Floymour</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>24052943443</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>L235811</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/gasparleigh_floor_lamp/L235811.html</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/L235811-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/L235811-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/L235811-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/L235811-SWATCH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>With a touch of mid-century influence and contemporary flair, the striking Gasparleigh floor lamp is illuminating in more ways than one. Its mix of faux wood with metal accents is fresh and modern, while a 3-way switch makes it quite accommodating.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Brown/Gold Finish</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>259.99</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Gasparleigh</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>24052933475</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T737-6</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/kallari_end_table/T737-6.html</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/T737-6-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T737-6-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T737-6-ALT-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T737-6-SLAT-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T737-6-FINISH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Double down on casual chic with the two-tone look of the Kallari end table. With its warm brown and matte black finishes, it reflects your eye for modern design. The trend-right slatted styling on the base brings added charm.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Warm Brown/Black</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Kallari</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>024052944938</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>23.63"</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>23.63" W x 23.63" D x 25.00" H</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>25.00"</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>23.63"</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3020414</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3130414</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3130514</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2890414</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>5710214</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PC3200514</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4860214</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>5980314</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PC3200614</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>A4000646</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/wrenlane_accent_table/A4000646.html</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/A4000646-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000646-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000646-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000646-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000646-FINISH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Make a big impact with the stunning Wrenlane accent table. The elegant all-marble construction and sculptural base create a contemporary aesthetic that's sure to make an impression. It's drop-dead gorgeous and functional, completing your seating arrangement with sophisticated style.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Black/White/Taupe</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>249.99</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Wrenlane</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>024052915815</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>15.00"</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>15.00" W x 15.00" D x 23.38" H</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>23.38"</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>15.00"</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A4000648</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/deaconwell_accent_table/A4000648.html</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/A4000648-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000648-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000648-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000648-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000648-FINISH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Elevate your space with exquisite natural beauty. With its sleek design and unique green veining, the Deaconwell marble accent table is a standout piece that effortlessly blends with contemporary decor. Perfect for placing next to your couch or bed, this functional and stylish table is ideal for holding your favorite book or a cup of coffee.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>White/Green</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>219.99</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Deaconwell</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>024052915839</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>14.00"</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>14.00" W x 14.00" D x 21.75" H</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>21.75"</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>14.00"</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PCP007-898</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T539-3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/vandenmore_end_table/T539-3.html</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/T539-3-CLSD-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T539-3-ANGLE-CLSD-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T539-3-ANGLE-OPEN-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T539-3-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T539-3-BACK-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T539-3-OPEN-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T539-3-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T539-1-3-FINISH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>The timeless styling of the Vandenmore end table is well-suited to casual and farmhouse-inspired spaces. Its versatile burnished brown finish seamlessly pairs with neutrals and muted tones alike. With drawers for sofa-side storage and a bottom shelf for displaying decor, this chic table beautifully suits everyday living.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Medium Brown</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Vandenmore</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>024052948660</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>R407071</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/jossler_8_x_10_rug/R407071.html</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/R407072-1-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407072-1-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407072-1-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407072-1-ROLL-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>An on-trend take on traditional stylings, the Jossler rug brings a pop of pattern underfoot. Simply soothing shades of ivory, brown and teal complement so many settings and color schemes. It’s an inviting addition to your home accents.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Ivory/Brown/Teal</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Jossler</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>024052913965</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T686-7</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/torlanta_chairside_end_table/T686-7.html</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/T686-7.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T686-7-ANGLE-CLSD-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T686-7-ANGLE-OPEN-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T686-7-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T686-7-SIDE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T686-7-BACK-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T686-7-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T686-7-WIRELESS-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T686-FINISH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Made for the everyday, the Torlanta chairside end table is a sleek complement to your casual contemporary living room. You’ll love the refined-yet-relaxed vibe of its contrasting medium brown finish and matte black legs. Simultaneously store and display decor behind the glass-front door. And for added function, a wireless charger keeps your tabletop free of clutter-causing cords.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>229.99</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Torlanta</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>024052895735</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T551-6</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/marstream_end_table/T551-6.html</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/T551-6-CLSD.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T551-6-ANGLE-CLSD-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T551-6-ANGLE-OPEN-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T551-6-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T551-6-SIDE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T551-6-OPEN.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T551-6-DRW-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T551-6-REED-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T551-8-6-FINISH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Classic and cool in dark charcoal, the Marstream end table brings contemporary convenience to your living room. Short on storage? The trendy reeded apron conceals a drawer perfect for remotes, controllers and other entertainment accessories. What a perfect marriage of style and functionality.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>229.99</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Marstream</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>024052903102</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T632-2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/montia_end_table/T632-2.html</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/T632-2.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T632-2-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T632-2-ANGLE-ALT-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T632-2-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T632-2-TOP-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T632-2-TILE-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T632-8-2-FINISH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Crafted with the utmost attention to detail, the Montia end table boasts premium materials that ensure both durability and elegance. The tabletop's sintered stone tile not only creates a visually appealing look but also enhances the table's robustness. Whether you're hosting guests or unwinding with a steaming cup of coffee, this table instantly adds a touch of sophistication to your living space.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Multi</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>229.99</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Montia</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>024052902853</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EB3660-114</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/calverson_king_platform_bed/EB3660-114.html</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/EB3660-114.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/EB3660-114-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/EB3660-114-ANGLE-NM-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/EB3660-114-BACK-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/EB3660-114-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/EB3660-114-SIDE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/EB3660-FINISH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>At the intersection of classic cool and chic sophistication you’ll find the Calverson king platform bed. The rich brown finish over replicated walnut wood grain offers an authentic touch that plays well any way you style it. Minimal yet elegant in its design, this bed keeps your home decor grounded while elevating your modern style.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>249.99</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Calverson</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>024052931341</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PCP587-703</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>7490914</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>6310114</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>R407652</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/dot_5_x_7_area_rug/R407652.html</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/R407652-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407652-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407652-1-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407652-1-ROLL-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407652-SWATCH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Infuse your home with warmth and energy. The inviting warm hues of the Dot area rug create a welcoming vibe, while the geometric design details add visual appeal galore. It's the perfect way to personalize your home and express your unique style. Wonderfully soft, this hand-tufted rug is a labor of love.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Cream/Brown/Taupe</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>229.99</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dot</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>024052944327</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>82.25"</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>59.75" W x 82.25" D x 0.50" H</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0.50"</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>59.75"</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>R407572</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/eldonmore_5_x_7_area_rug/R407572.html</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/R407572-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407572-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407572-1-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407572-1-ROLL-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407572-SWATCH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Rocking a stylish geometric design, the elegant Eldonmore area rug knows how to make a statement. Its black and ivory pattern offers a welcome complement underfoot that doesn’t overtake your room’s design. You’ll love how the rug adds a contemporary touch under a couch or bed.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Black/Ivory</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>229.99</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Eldonmore</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>024052944228</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>81.75"</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>59.50" W x 81.75" D x 0.50" H</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>0.50"</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>59.50"</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>R407202</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/perrenton_5_x_7_rug/R407202.html</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/R407202-1-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407202-1-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407202-1-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407202-1-ROLL-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>The exquisitely hand-tufted Perrenton rug invites you to indulge in marvelously modern style. Its warm, earthy palette and geometric design give you a beautiful room that looks and feels finished. That makes us smile—how about you?</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Perrenton</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>024052914122</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>85.50"</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>61.25" W x 85.50" D x 0.50" H</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>0.50"</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>61.25"</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T135-13</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/lyncott_table_set_of_3/T135-13.html</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/T135-13.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T135-13-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T135-13-CT-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T135-13-END-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T135-13-CT-ANGLE-ALT-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T135-13-CT-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T135-13-END-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T135-13-CT-TOP-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T135-13-CT-TOP-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T135-13-END-TOP-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T135-13-MOOD.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T135-13-ET-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/T135-13-CT-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>A refreshed take on retro aesthetics. The Lyncott table set adds an air of playful simplicity to your home, capturing the architectural language of mid-century stylings. Subtly dynamic in design, the tables invite the eye with geometric tops. A casual, yet timeless, medium brown finish completes this study in form and function.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lyncott</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>024052934632</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>28.00"</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>42.00" W x 28.00" D x 18.00" H</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>18.00"</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>42.00"</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A3000750</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/vavuniya_storage_bench/A3000750.html</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/A3000750-CLSD-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A3000750-ANGLE-CLSD-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A3000750-ANGLE-OPEN-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A3000750-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A3000750-OPEN-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A3000750-SWATCH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>There’s more to the Vavuniya upholstered storage bench than what meets the eye. Its soft heathered brown upholstery provides a comfy sitting area. Lift the hinged seat to reveal lots of storage for pillows, blankets or other essentials. Coupled with its unique capsule shape, this bench is full of form and function.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>219.99</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Vavuniya</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>024052942903</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>18.00"</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>55.63" W x 18.00" D x 19.00" H</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>19.00"</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>55.63"</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>A4000717</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/dallenburg_accent_table/A4000717.html</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/A4000717-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000717-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000717-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000717-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000717-FINISH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>The Dallenburg accent table is a monochromatic, metallic take on sofa-side function. Dressed up in a goldtone finish, it stylishly keeps entertainment essentials and refreshments close. Need a stand to showcase decor? This table acts as a luxe landing place for an elegant houseplant or a statement-making accent. Contemporary glam has never looked so good.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Gold Finish</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>229.99</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dallenburg</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>024052943184</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>12.50"</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>12.50" W x 12.50" D x 24.00" H</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>24.00"</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>12.50"</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>L329111</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/ailsa_floor_lamp/L329111.html</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/L329111-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/L329111-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/L329111-DETAIL-ALT.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/L329111-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/L329111-SWATCH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Seamlessly bridge casual craftsmanship and organic beauty with the Ailsa floor lamp. The modern profile of its sculptural wooden base elevates the relaxed vibe of the rich natural brown finish. Place this lamp in an office corner, or between sofas in a seating area, for a dose of everyday elegance.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Natural Brown</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>229.99</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ailsa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>024052943979</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>18.13"</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>18.13" W x 18.13" D x 60.25" H</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>60.25"</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>18.13"</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>R407852</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/azelhurst_5_x_7_area_rug/R407852.html</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/R407852-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407852-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407852-1-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407852-1-ROLL-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407852-SWATCH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Soft, serene style. The Azelhurst area rug combines the comfort of hand tufted wool with the soothing feel of coastal casual aesthetics. Its detailed border design, in a palette of blue, ivory and gray, welcomes with relaxed character.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Blue/Ivory/Gray</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>219.99</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Azelhurst</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>024052944600</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>82.75"</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>59.50" W x 82.75" D x 0.50" H</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>0.50"</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>59.50"</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>R407762</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/rizwana_5_x_7_area_rug/R407762.html</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/R407762-4X3-CROP.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407762-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407762-1-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407762-1-ROLL-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/R407762-SWATCH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Crafted with hand tufted wool for an ultra-plush feel, the Rizwana area rug appeals to your contemporary sensibilities. An abstract ripple pattern incorporates subtle movement and a calming air into your decor. The rug's hues of ivory, brown and gray lend a modern versatility.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Ivory/Brown/Gray</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>219.99</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Rizwana</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>024052944525</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>85.75"</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>62.00" W x 85.75" D x 0.75" H</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>0.75"</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>62.00"</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>A4000623</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://www.ashleyfurniture.com/p/henfield_accent_table/A4000623.html</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://cdn.ashley.com/assets/A4000623.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000623-ANGLE-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000623-HEAD-ON-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000623-TOP-SW-P1-KO.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000623-TOP-DETAIL.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg | https://cdn.ashley.com/assets/A4000623-TOP-FINISH-500.jpg?width=310&amp;height=204&amp;fit=cover&amp;quality=100&amp;format=jpeg</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Simply elegant. The Henfield accent table combines the beauty of wood and stone, appealing to the luxurious but inviting vibe of your contemporary aesthetic. A beige marble top pairs with cylindrical legs in a brown finish, giving this refined piece an aura of welcoming warmth. It’s a homey take on highbrow design, balancing approachable character with your taste for elevated styling.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Beige/Brown</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>179.99</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Henfield</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>024052871555</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>A4000624</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>A8000506</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>R407302</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>R407282</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>R407292</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>R407312</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>R407122</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>A8000432</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>A4000724</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>T513-3</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>T712-2</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>T622-2</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>R407051</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>R407041</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>R407812</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>R407702</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>R407662</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>R407842</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>R407642</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>T623-6</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PCB386-92</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>R407622</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>R407532</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>R407421</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>R407791</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>A8000501</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>A8000498</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>A4000722</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>A3000744</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>M20111</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>A8000448</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>PCB1170-92</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>R407482</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>R407492</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>T656-3</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>D974-324</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>R407522</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>A8000500</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>A8000440</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>A8000442</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>A8000490</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>PCB1580-92</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>L207644</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>R407132</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>A8000439</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>R407371</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>R407401</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>L207514</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>L207574</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>A8000495</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>A8000486</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>A8000463</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>A4000716</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>L235861</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>A2000768</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>R407092</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>R407632</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>A8000487</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>A8000480</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>A8000502</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>A4000661</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>A8000453</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>A8000454</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>A8000451</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>A8000474</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>A8000459</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>A8000457</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>L430914</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>L207624</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>T190-317</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>T190-117</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>T190-217</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>PCP803-702</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>L100814</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>R407452</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>R407462</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>R407442</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>A8000489</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>A8000504</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>L430884</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>L207524</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>A2000748</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>A8000461</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>A8000473</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>A8000472</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>A8000464</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>A8000450</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>A4000720</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>L235954</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>L430894</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>L235921</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>L235874</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>A8000483</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>L431604</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>L207564</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>A8000475</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>A8000465</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>A8000460</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>A8000476</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>PCB1819-01</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>L208461</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>L207604</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>L207614</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>L429094</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>R407592</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>A1001083</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>L207504</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>A2000747</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>R407212</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>R407332</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>R407222</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>L207634</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>L235974</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>L100834</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>L430864</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>L430874</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>L429084</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>R407752</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>R407682</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>L100804</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>R407172</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>R407182</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>A8000455</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>L207534</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>L207594</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>L208434</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>L208444</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>L235984</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>PCD824-07</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>PCD824-01</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>PCD373-03</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>R407552</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>R407692</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>L235824</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>L235854</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
